--- a/7.더마을에프앤비/산출물_2025/요구사항추적표_더마을에프앤비.xlsx
+++ b/7.더마을에프앤비/산출물_2025/요구사항추적표_더마을에프앤비.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\60_document\정부과제문서\2025년도사업문서\7.더마을에프앤비\산출물_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8963D85B-1CF5-4506-B6FE-CB821A2ED641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DDDE5A-889E-46FB-B1A1-4DF9789CE9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>요구사항명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -342,66 +342,125 @@
     <t>SMMES-AD2-008</t>
   </si>
   <si>
+    <t>SMMES-AD2-010</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-011</t>
+  </si>
+  <si>
+    <t>로그인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콜드체인 대시보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-001-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-001-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-001-03</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-002-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-002-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-003-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-003-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-004-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-004-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-004-03</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-004-04</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-005-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-005-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-006-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-006-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-007-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-007-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-008-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-008-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-008-03</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-008-04</t>
+  </si>
+  <si>
     <t>SMMES-AD2-009</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-010</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-011</t>
-  </si>
-  <si>
-    <t>로그인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>콜드체인 대시보드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-001-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-001-02</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-001-03</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-002-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-002-02</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-003-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-003-02</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-004-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMMES-AD2-004-02</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-004-03</t>
-  </si>
-  <si>
-    <t>SMMES-AD2-004-04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-009-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-009-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-010-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-010-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-011-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMMES-AD2-011-02</t>
+  </si>
+  <si>
+    <t>SMMES-AD2-011-03</t>
   </si>
 </sst>
 </file>
@@ -495,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -513,9 +572,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -809,7 +865,7 @@
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
     <col min="2" max="2" width="15.125" customWidth="1"/>
-    <col min="3" max="3" width="20" style="13" customWidth="1"/>
+    <col min="3" max="3" width="20" style="12" customWidth="1"/>
     <col min="4" max="4" width="18.25" customWidth="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
     <col min="6" max="8" width="18.25" customWidth="1"/>
@@ -850,13 +906,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="C2" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
@@ -867,7 +923,9 @@
       <c r="F2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -876,7 +934,7 @@
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
@@ -894,7 +952,7 @@
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
@@ -913,10 +971,10 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>33</v>
@@ -927,7 +985,9 @@
       <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -936,7 +996,7 @@
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
@@ -958,7 +1018,7 @@
         <v>78</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
@@ -969,7 +1029,9 @@
       <c r="F7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>5</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -978,7 +1040,7 @@
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
@@ -1000,7 +1062,7 @@
         <v>79</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>39</v>
@@ -1011,7 +1073,9 @@
       <c r="F9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>7</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1020,7 +1084,7 @@
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
@@ -1036,7 +1100,7 @@
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
@@ -1052,7 +1116,7 @@
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
@@ -1073,7 +1137,9 @@
       <c r="B13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="11"/>
+      <c r="C13" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1083,7 +1149,9 @@
       <c r="F13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1091,7 +1159,9 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="11"/>
+      <c r="C14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
         <v>22</v>
@@ -1109,7 +1179,9 @@
       <c r="B15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="11"/>
+      <c r="C15" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
@@ -1119,7 +1191,9 @@
       <c r="F15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1127,7 +1201,9 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="11"/>
+      <c r="C16" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
@@ -1145,7 +1221,9 @@
       <c r="B17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="D17" s="3" t="s">
         <v>55</v>
       </c>
@@ -1155,7 +1233,9 @@
       <c r="F17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>13</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1163,7 +1243,9 @@
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="11"/>
+      <c r="C18" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
         <v>23</v>
@@ -1176,12 +1258,14 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="11"/>
+      <c r="C19" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="D19" s="3" t="s">
         <v>58</v>
       </c>
@@ -1191,7 +1275,9 @@
       <c r="F19" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>15</v>
+      </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1199,7 +1285,9 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="11"/>
+      <c r="C20" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
         <v>24</v>
@@ -1213,7 +1301,9 @@
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="11"/>
+      <c r="C21" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1227,7 +1317,9 @@
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="11"/>
+      <c r="C22" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3" t="s">
         <v>37</v>
@@ -1245,9 +1337,11 @@
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="11"/>
+        <v>111</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="D23" s="3" t="s">
         <v>63</v>
       </c>
@@ -1257,7 +1351,9 @@
       <c r="F23" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>19</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1265,7 +1361,9 @@
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="11"/>
+      <c r="C24" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
         <v>65</v>
@@ -1281,9 +1379,11 @@
         <v>67</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="11"/>
+        <v>84</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="D25" s="3" t="s">
         <v>68</v>
       </c>
@@ -1293,7 +1393,9 @@
       <c r="F25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>20</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1301,7 +1403,9 @@
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="11"/>
+      <c r="C26" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
         <v>71</v>
@@ -1319,9 +1423,11 @@
         <v>72</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="11"/>
+        <v>85</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="D27" s="3" t="s">
         <v>73</v>
       </c>
@@ -1331,7 +1437,9 @@
       <c r="F27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>22</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1339,7 +1447,9 @@
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
-      <c r="C28" s="11"/>
+      <c r="C28" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
         <v>76</v>
@@ -1355,7 +1465,9 @@
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
-      <c r="C29" s="11"/>
+      <c r="C29" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
         <v>77</v>
@@ -1371,7 +1483,7 @@
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="12"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="6"/>
     </row>
   </sheetData>

--- a/7.더마을에프앤비/산출물_2025/요구사항추적표_더마을에프앤비.xlsx
+++ b/7.더마을에프앤비/산출물_2025/요구사항추적표_더마을에프앤비.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\60_document\정부과제문서\2025년도사업문서\7.더마을에프앤비\산출물_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DDDE5A-889E-46FB-B1A1-4DF9789CE9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5D76A3-454F-4C5E-84F5-79F0E1C588E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="산출물목록" sheetId="2" r:id="rId1"/>
+    <sheet name="요구사항추적표" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>요구사항명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -461,13 +462,53 @@
   </si>
   <si>
     <t>SMMES-AD2-011-03</t>
+  </si>
+  <si>
+    <t>★2 SS-AD2 요구사항정의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★1 SS-AD1 현행업무분석_선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★3 SS-AD3 기능명세서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★4 SS-TD1 개선업무설계서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★5 SS-TD2 아키텍처설계서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★6 SS-TD3 화면설계서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★7 SS-TD4 프로그램설계서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>★8 SS-TD5 데이터베이스설계서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔젤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더마을에프앤비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +553,20 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -554,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -578,6 +633,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -859,6 +925,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8D90DA-4A4C-4783-A762-7CFF5DA71F9C}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46.75" style="13" customWidth="1"/>
+    <col min="2" max="5" width="27" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="14"/>
+      <c r="B1" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+    </row>
+    <row r="3" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="17">
+        <v>45910</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="17">
+        <v>45930</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="17">
+        <v>45935</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="17">
+        <v>45940</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="17">
+        <v>45945</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="17">
+        <v>45960</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="17">
+        <v>45960</v>
+      </c>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:3" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="17" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
